--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488218_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488218_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9886</v>
+        <v>7.0604</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5841</v>
+        <v>4.5626</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4045</v>
+        <v>2.4979</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7097</v>
+        <v>4.9304</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4284</v>
+        <v>0.8461</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2813</v>
+        <v>4.0843</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2744</v>
+        <v>4.0219</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1393</v>
+        <v>0.8287</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1351</v>
+        <v>3.1933</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5647</v>
+        <v>0.9085</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7108</v>
+        <v>0.0174</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1462</v>
+        <v>0.891</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.7793</v>
+        <v>1.1117</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.8175</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>7.3732</v>
+        <v>1.3328</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5539</v>
+        <v>0.5406</v>
       </c>
       <c r="U2" t="n">
-        <v>2.8193</v>
+        <v>0.7921</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.315</v>
+        <v>-0.3144</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.8883</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8535</v>
+        <v>4.1884</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6265</v>
+        <v>2.7441</v>
       </c>
       <c r="F3" t="n">
-        <v>2.227</v>
+        <v>1.4443</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9304</v>
+        <v>3.7097</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8461</v>
+        <v>3.4284</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0843</v>
+        <v>0.2813</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0219</v>
+        <v>4.2744</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8287</v>
+        <v>4.1393</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1933</v>
+        <v>0.1351</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9085</v>
+        <v>-0.5647</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0174</v>
+        <v>-0.7108</v>
       </c>
       <c r="O3" t="n">
-        <v>0.891</v>
+        <v>0.1462</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1117</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.8175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1258</v>
+        <v>3.573</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3954</v>
+        <v>1.7139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5213</v>
+        <v>1.8591</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3144</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7818</v>
+        <v>2.301</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5279</v>
+        <v>0.1144</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3097</v>
+        <v>2.1866</v>
       </c>
       <c r="G4" t="n">
         <v>1.742</v>
@@ -766,13 +766,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5956</v>
+        <v>1.1148</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1977</v>
+        <v>0.4446</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7934</v>
+        <v>0.6703</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0548</v>
+        <v>0.3698</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.872</v>
+        <v>-0.9152</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8172</v>
+        <v>1.285</v>
       </c>
       <c r="G6" t="n">
         <v>1.62</v>
@@ -922,13 +922,13 @@
         <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9399</v>
+        <v>1.3645</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4514</v>
+        <v>0.4082</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4884</v>
+        <v>0.9563</v>
       </c>
       <c r="V6" t="n">
         <v>2.2027</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4208</v>
+        <v>-1.3716</v>
       </c>
       <c r="E7" t="n">
         <v>-2.3213</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9004</v>
+        <v>0.9497</v>
       </c>
       <c r="G7" t="n">
         <v>-1.302</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0664</v>
+        <v>0.1156</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2853</v>
+        <v>0.3345</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9554</v>
+        <v>-1.9056</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1891</v>
+        <v>-1.287</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7664</v>
+        <v>-0.6186</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5255</v>
@@ -1078,13 +1078,13 @@
         <v>0.3706</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7178</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6193</v>
+        <v>0.5214</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0985</v>
+        <v>0.2462</v>
       </c>
       <c r="V8" t="n">
         <v>-2.5183</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0195</v>
+        <v>-2.7471</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8345</v>
+        <v>-2.0943</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1849</v>
+        <v>-0.6528</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8394</v>
+        <v>2.1118</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.8335</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7461</v>
+        <v>1.2783</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8883</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6817</v>
+        <v>-3.773</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9466</v>
+        <v>-4.1857</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2649</v>
+        <v>0.4127</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2087</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4355</v>
+        <v>0.3441</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1131</v>
+        <v>-0.3522</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5486</v>
+        <v>0.6964</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7996</v>
+        <v>-4.2115</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9779</v>
+        <v>-5.4883</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1783</v>
+        <v>1.2768</v>
       </c>
       <c r="G11" t="n">
         <v>-4.343</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0861</v>
+        <v>0.5021</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9302</v>
+        <v>-0.4405</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8441</v>
+        <v>0.9426</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5081</v>
+        <v>-4.4533</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0041</v>
+        <v>-5.3186</v>
       </c>
       <c r="F12" t="n">
-        <v>0.496</v>
+        <v>0.8653</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5714</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3432</v>
+        <v>0.7116</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.909</v>
+        <v>-0.2235</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5658</v>
+        <v>0.9351</v>
       </c>
       <c r="V12" t="n">
         <v>1.2594</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.193899999999998</v>
+        <v>-3.920400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.8407</v>
+        <v>-13.5672</v>
       </c>
       <c r="F13" t="n">
-        <v>9.646700000000001</v>
+        <v>9.6469</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9264</v>
@@ -1468,13 +1468,13 @@
         <v>12.0438</v>
       </c>
       <c r="S13" t="n">
-        <v>11.6643</v>
+        <v>11.9379</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9536</v>
+        <v>3.2271</v>
       </c>
       <c r="U13" t="n">
-        <v>8.710799999999999</v>
+        <v>8.710899999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8883</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,37 +1501,37 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2041</v>
+        <v>4.9545</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3718</v>
+        <v>3.4279</v>
       </c>
       <c r="F14" t="n">
-        <v>5.5759</v>
+        <v>1.5266</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3681</v>
+        <v>2.7893</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7138</v>
+        <v>0.7498</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6543</v>
+        <v>2.0395</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9728</v>
+        <v>3.3369</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1635</v>
+        <v>2.1424</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8093</v>
+        <v>1.1945</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3953</v>
+        <v>-0.5477</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4497</v>
+        <v>-1.3927</v>
       </c>
       <c r="O14" t="n">
         <v>0.845</v>
@@ -1540,34 +1540,34 @@
         <v>2.7793</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>4.6322</v>
+        <v>3.7057</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2572</v>
+        <v>-2.377</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8056</v>
+        <v>-1.5003</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5484</v>
+        <v>-0.8767</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3139</v>
+        <v>1.7629</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3139</v>
+        <v>2.5177</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,37 +1579,37 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.202</v>
+        <v>4.2591</v>
       </c>
       <c r="E15" t="n">
-        <v>3.232</v>
+        <v>-1.078</v>
       </c>
       <c r="F15" t="n">
-        <v>0.97</v>
+        <v>5.3371</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7893</v>
+        <v>2.3681</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7498</v>
+        <v>0.7138</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0395</v>
+        <v>1.6543</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3369</v>
+        <v>1.9728</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1424</v>
+        <v>1.1635</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1945</v>
+        <v>0.8093</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5477</v>
+        <v>0.3953</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3927</v>
+        <v>-0.4497</v>
       </c>
       <c r="O15" t="n">
         <v>0.845</v>
@@ -1618,34 +1618,34 @@
         <v>2.7793</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>3.7057</v>
+        <v>4.6322</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.1295</v>
+        <v>-1.2022</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6962</v>
+        <v>-1.5118</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4333</v>
+        <v>0.3096</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7629</v>
+        <v>0.3139</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5177</v>
+        <v>0.3139</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.012</v>
+        <v>2.7138</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.702</v>
+        <v>0.7864</v>
       </c>
       <c r="F16" t="n">
-        <v>3.714</v>
+        <v>1.9273</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4033</v>
+        <v>0.3313</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5384</v>
+        <v>1.0486</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9417</v>
+        <v>-0.7173</v>
       </c>
       <c r="J16" t="n">
-        <v>0.191</v>
+        <v>0.5598</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0993</v>
+        <v>1.0776</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2903</v>
+        <v>-0.5178</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2123</v>
+        <v>-0.2285</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4391</v>
+        <v>-0.029</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6514</v>
+        <v>-0.1996</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1499</v>
+        <v>2.2234</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>4.0763</v>
+        <v>3.1499</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2141</v>
+        <v>-0.4704</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.281</v>
+        <v>-0.7352</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4951</v>
+        <v>0.2649</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7553</v>
+        <v>0.6294</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>1.8883</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0697</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>J. CAMPOS CAMPOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9755</v>
+        <v>2.6901</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0802</v>
+        <v>-0.0964</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8953</v>
+        <v>2.7865</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3313</v>
+        <v>0.7146</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0486</v>
+        <v>-1.0933</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7173</v>
+        <v>1.8079</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5598</v>
+        <v>-0.0113</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0776</v>
+        <v>-0.1677</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5178</v>
+        <v>0.1565</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2285</v>
+        <v>0.7259</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.029</v>
+        <v>-0.9255</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1996</v>
+        <v>1.6514</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1499</v>
+        <v>3.5205</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2087</v>
+        <v>-2.0845</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4414</v>
+        <v>-1.3794</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2328</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6294</v>
+        <v>2.3924</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8883</v>
+        <v>3.1471</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2589</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CAMPOS CAMPOS</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0109</v>
+        <v>2.1199</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1943</v>
+        <v>-1.3875</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2053</v>
+        <v>3.5074</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7146</v>
+        <v>0.4033</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0933</v>
+        <v>-1.5384</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8079</v>
+        <v>1.9417</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0113</v>
+        <v>0.191</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1677</v>
+        <v>-0.0993</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1565</v>
+        <v>0.2903</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7259</v>
+        <v>0.2123</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9255</v>
+        <v>-1.4391</v>
       </c>
       <c r="O18" t="n">
         <v>1.6514</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6676</v>
+        <v>3.1499</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5205</v>
+        <v>4.0763</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.7636</v>
+        <v>-0.678</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4773</v>
+        <v>-0.9665</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2863</v>
+        <v>0.2885</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3924</v>
+        <v>-0.7553</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1471</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7548</v>
+        <v>-1.0697</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4472</v>
+        <v>0.8646</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1019</v>
+        <v>-0.906</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5491</v>
+        <v>1.7707</v>
       </c>
       <c r="G19" t="n">
         <v>1.1575</v>
@@ -1936,13 +1936,13 @@
         <v>3.3352</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5447</v>
+        <v>-1.1273</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3679</v>
+        <v>-1.172</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1768</v>
+        <v>0.0448</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5744</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5215</v>
+        <v>-2.5708</v>
       </c>
       <c r="E20" t="n">
         <v>-2.5057</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0158</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-2.434</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8287</v>
+        <v>-0.8779</v>
       </c>
       <c r="T20" t="n">
         <v>-0.5471</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2815</v>
+        <v>-0.3308</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7286</v>
+        <v>-3.3278</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3784</v>
+        <v>-2.2804</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3503</v>
+        <v>-1.0473</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4432</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2157</v>
+        <v>-0.8148</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6685</v>
+        <v>-0.3656</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4403</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4075</v>
+        <v>-6.2037</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7048</v>
+        <v>-5.6069</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7027</v>
+        <v>-0.5968</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9605</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9304</v>
+        <v>-0.7265</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3833</v>
+        <v>-0.2773</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4403</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.1941</v>
+        <v>5.499699999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.646699999999999</v>
+        <v>-9.646599999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>13.8408</v>
+        <v>15.1464</v>
       </c>
       <c r="G23" t="n">
-        <v>1.926399999999999</v>
+        <v>1.9264</v>
       </c>
       <c r="H23" t="n">
         <v>-5.599900000000001</v>
@@ -2224,7 +2224,7 @@
         <v>3.2418</v>
       </c>
       <c r="K23" t="n">
-        <v>1.131400000000001</v>
+        <v>1.1314</v>
       </c>
       <c r="L23" t="n">
         <v>2.1106</v>
@@ -2233,7 +2233,7 @@
         <v>-1.3155</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.7312</v>
+        <v>-6.731199999999999</v>
       </c>
       <c r="O23" t="n">
         <v>5.4157</v>
@@ -2248,16 +2248,16 @@
         <v>24.0874</v>
       </c>
       <c r="S23" t="n">
-        <v>-11.6644</v>
+        <v>-10.3586</v>
       </c>
       <c r="T23" t="n">
-        <v>-8.710700000000001</v>
+        <v>-8.710699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.9534</v>
+        <v>-1.6477</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8883</v>
+        <v>1.888299999999999</v>
       </c>
       <c r="W23" t="n">
         <v>7.8659</v>
